--- a/outputs/Block5B_Senate_State_Model_CV.xlsx
+++ b/outputs/Block5B_Senate_State_Model_CV.xlsx
@@ -524,10 +524,10 @@
         <v>22</v>
       </c>
       <c r="G3">
-        <v>10.67099907079506</v>
+        <v>11.68950373246543</v>
       </c>
       <c r="H3">
-        <v>1.671469422903677</v>
+        <v>0.6529647612333118</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -550,16 +550,16 @@
         <v>23</v>
       </c>
       <c r="G4">
-        <v>10.67099907079506</v>
+        <v>10.75322793133383</v>
       </c>
       <c r="H4">
-        <v>1.671469422903677</v>
+        <v>1.589240562364909</v>
       </c>
       <c r="I4">
-        <v>0.9651456379123636</v>
+        <v>0.9764487606055239</v>
       </c>
       <c r="J4">
-        <v>5.883232315516177</v>
+        <v>5.416213044670446</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -608,10 +608,10 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>-24.36362353680956</v>
+        <v>-21.73515267677366</v>
       </c>
       <c r="H6">
-        <v>6.233753406939432</v>
+        <v>3.605282546903531</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -692,10 +692,10 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>9.254734841897383</v>
+        <v>9.1637449066593</v>
       </c>
       <c r="H9">
-        <v>2.433370569042802</v>
+        <v>2.342380633804719</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -718,16 +718,16 @@
         <v>23</v>
       </c>
       <c r="G10">
-        <v>9.651894504917014</v>
+        <v>10.0035592003176</v>
       </c>
       <c r="H10">
-        <v>2.830530232062433</v>
+        <v>3.182194927463021</v>
       </c>
       <c r="I10">
-        <v>0.9644598621575147</v>
+        <v>0.9791016028618784</v>
       </c>
       <c r="J10">
-        <v>5.347415870950532</v>
+        <v>4.91445526193885</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -776,10 +776,10 @@
         <v>22</v>
       </c>
       <c r="G12">
-        <v>-9.955940524015368</v>
+        <v>-11.31966445305881</v>
       </c>
       <c r="H12">
-        <v>3.842883995751237</v>
+        <v>5.206607924794682</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -802,16 +802,16 @@
         <v>23</v>
       </c>
       <c r="G13">
-        <v>-9.559005602216548</v>
+        <v>-11.31966445305881</v>
       </c>
       <c r="H13">
-        <v>3.445949073952416</v>
+        <v>5.206607924794682</v>
       </c>
       <c r="I13">
-        <v>0.03700245138239838</v>
+        <v>0.03127544667373272</v>
       </c>
       <c r="J13">
-        <v>5.350440096094329</v>
+        <v>6.078095009157831</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -860,10 +860,10 @@
         <v>22</v>
       </c>
       <c r="G15">
-        <v>-17.56764752317505</v>
+        <v>-14.94716851103501</v>
       </c>
       <c r="H15">
-        <v>5.550480141200801</v>
+        <v>2.930001129060766</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -944,10 +944,10 @@
         <v>22</v>
       </c>
       <c r="G18">
-        <v>1.204858019955478</v>
+        <v>0.3802548163930437</v>
       </c>
       <c r="H18">
-        <v>2.828504980821412</v>
+        <v>2.003901777258977</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -970,16 +970,16 @@
         <v>23</v>
       </c>
       <c r="G19">
-        <v>1.345291479820631</v>
+        <v>0.8627731481068373</v>
       </c>
       <c r="H19">
-        <v>2.968938440686564</v>
+        <v>2.486420108972771</v>
       </c>
       <c r="I19">
-        <v>0.5564220201073067</v>
+        <v>0.5650394724382881</v>
       </c>
       <c r="J19">
-        <v>9.480303448039768</v>
+        <v>5.268561684149072</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1028,10 +1028,10 @@
         <v>22</v>
       </c>
       <c r="G21">
-        <v>-8.444529015258723</v>
+        <v>-9.800259899000016</v>
       </c>
       <c r="H21">
-        <v>5.140857132268032</v>
+        <v>6.496588016009325</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1054,16 +1054,16 @@
         <v>23</v>
       </c>
       <c r="G22">
-        <v>-7.951350832425254</v>
+        <v>-9.800259899000016</v>
       </c>
       <c r="H22">
-        <v>4.647678949434562</v>
+        <v>6.496588016009325</v>
       </c>
       <c r="I22">
-        <v>0.06692398885461097</v>
+        <v>0.05562120441023274</v>
       </c>
       <c r="J22">
-        <v>5.304086907287133</v>
+        <v>6.153493076600435</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1112,10 +1112,10 @@
         <v>22</v>
       </c>
       <c r="G24">
-        <v>18.46085294421424</v>
+        <v>18.31905731255421</v>
       </c>
       <c r="H24">
-        <v>2.519119217006342</v>
+        <v>2.377323585346311</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1138,16 +1138,16 @@
         <v>23</v>
       </c>
       <c r="G25">
-        <v>18.46085294421424</v>
+        <v>16.92748453157387</v>
       </c>
       <c r="H25">
-        <v>2.519119217006342</v>
+        <v>0.9857508043659706</v>
       </c>
       <c r="I25">
         <v>0.999</v>
       </c>
       <c r="J25">
-        <v>5.948865361881026</v>
+        <v>5.097629839420638</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>22</v>
       </c>
       <c r="G27">
-        <v>14.40930571032542</v>
+        <v>14.91926043901995</v>
       </c>
       <c r="H27">
-        <v>0.5673211366335345</v>
+        <v>1.07727586532806</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1222,16 +1222,16 @@
         <v>23</v>
       </c>
       <c r="G28">
-        <v>14.54545454545455</v>
+        <v>14.73235749223725</v>
       </c>
       <c r="H28">
-        <v>0.703469971762658</v>
+        <v>0.8903729185453599</v>
       </c>
       <c r="I28">
-        <v>0.9424778302077692</v>
+        <v>0.9983850508270111</v>
       </c>
       <c r="J28">
-        <v>9.229820350813995</v>
+        <v>5.002555534632684</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1280,10 +1280,10 @@
         <v>22</v>
       </c>
       <c r="G30">
-        <v>13.84596845774055</v>
+        <v>13.90071227596027</v>
       </c>
       <c r="H30">
-        <v>7.214668722992533</v>
+        <v>7.269412541212256</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1306,16 +1306,16 @@
         <v>23</v>
       </c>
       <c r="G31">
-        <v>12.5527104080912</v>
+        <v>11.28682426755171</v>
       </c>
       <c r="H31">
-        <v>5.921410673343185</v>
+        <v>4.6555245328037</v>
       </c>
       <c r="I31">
-        <v>0.9802133371119082</v>
+        <v>0.980343280570425</v>
       </c>
       <c r="J31">
-        <v>6.098951576280304</v>
+        <v>5.4766720780999</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1364,10 +1364,10 @@
         <v>22</v>
       </c>
       <c r="G33">
-        <v>-30.09168861960553</v>
+        <v>-27.46616089753333</v>
       </c>
       <c r="H33">
-        <v>10.24789044881118</v>
+        <v>7.62236272673897</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1448,10 +1448,10 @@
         <v>22</v>
       </c>
       <c r="G36">
-        <v>-3.18930072759332</v>
+        <v>-5.551894403746672</v>
       </c>
       <c r="H36">
-        <v>4.639445449776709</v>
+        <v>2.276851773623356</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1474,16 +1474,16 @@
         <v>23</v>
       </c>
       <c r="G37">
-        <v>-2.991452991452995</v>
+        <v>-4.271673697599834</v>
       </c>
       <c r="H37">
-        <v>4.837293185917034</v>
+        <v>3.557072479770195</v>
       </c>
       <c r="I37">
-        <v>0.3817745054893844</v>
+        <v>0.2178221736430758</v>
       </c>
       <c r="J37">
-        <v>9.944209787481359</v>
+        <v>5.479529412288271</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1532,10 +1532,10 @@
         <v>22</v>
       </c>
       <c r="G39">
-        <v>0.003253271547104974</v>
+        <v>-1.970258657847667</v>
       </c>
       <c r="H39">
-        <v>2.796746728452892</v>
+        <v>4.770258657847664</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1558,16 +1558,16 @@
         <v>23</v>
       </c>
       <c r="G40">
-        <v>-0.3613854101650343</v>
+        <v>-1.970258657847667</v>
       </c>
       <c r="H40">
-        <v>3.161385410165031</v>
+        <v>4.770258657847664</v>
       </c>
       <c r="I40">
-        <v>0.4760880166957929</v>
+        <v>0.3882341621301975</v>
       </c>
       <c r="J40">
-        <v>6.02566232575385</v>
+        <v>6.939377955031237</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -1616,10 +1616,10 @@
         <v>22</v>
       </c>
       <c r="G42">
-        <v>-62.83119647919543</v>
+        <v>-65.17435072854664</v>
       </c>
       <c r="H42">
-        <v>6.361851870315945</v>
+        <v>8.705006119667161</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -1642,16 +1642,16 @@
         <v>23</v>
       </c>
       <c r="G43">
-        <v>-62.83119647919543</v>
+        <v>-67.27957794583672</v>
       </c>
       <c r="H43">
-        <v>6.361851870315945</v>
+        <v>10.81023333695724</v>
       </c>
       <c r="I43">
         <v>0.001</v>
       </c>
       <c r="J43">
-        <v>7.263203911640863</v>
+        <v>5.621628320182992</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1700,10 +1700,10 @@
         <v>22</v>
       </c>
       <c r="G45">
-        <v>-31.05493576886262</v>
+        <v>-26.25257461158482</v>
       </c>
       <c r="H45">
-        <v>5.919854147103752</v>
+        <v>10.72221530438156</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -1726,16 +1726,16 @@
         <v>23</v>
       </c>
       <c r="G46">
-        <v>-31.19658119658119</v>
+        <v>-28.72457790408301</v>
       </c>
       <c r="H46">
-        <v>5.778208719385184</v>
+        <v>8.25021201188337</v>
       </c>
       <c r="I46">
         <v>0.001</v>
       </c>
       <c r="J46">
-        <v>9.182678469311528</v>
+        <v>5.376703172437014</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -1784,10 +1784,10 @@
         <v>22</v>
       </c>
       <c r="G48">
-        <v>16.28594302101494</v>
+        <v>15.73957854638889</v>
       </c>
       <c r="H48">
-        <v>5.022969196988193</v>
+        <v>5.569333671614251</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -1810,16 +1810,16 @@
         <v>23</v>
       </c>
       <c r="G49">
-        <v>15.95008944966925</v>
+        <v>15.34105364101053</v>
       </c>
       <c r="H49">
-        <v>5.358822768333884</v>
+        <v>5.967858576992604</v>
       </c>
       <c r="I49">
-        <v>0.9956436158212228</v>
+        <v>0.9977967295084087</v>
       </c>
       <c r="J49">
-        <v>6.080571292031284</v>
+        <v>5.387569742141933</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -1868,10 +1868,10 @@
         <v>22</v>
       </c>
       <c r="G51">
-        <v>-35.22880802189839</v>
+        <v>-35.5447233573444</v>
       </c>
       <c r="H51">
-        <v>8.983028834340836</v>
+        <v>9.298944169786843</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -1894,16 +1894,16 @@
         <v>23</v>
       </c>
       <c r="G52">
-        <v>-35.22880802189839</v>
+        <v>-37.47192764550119</v>
       </c>
       <c r="H52">
-        <v>8.983028834340836</v>
+        <v>11.22614845794363</v>
       </c>
       <c r="I52">
         <v>0.001</v>
       </c>
       <c r="J52">
-        <v>5.712942512816499</v>
+        <v>5.030974372955976</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -1952,10 +1952,10 @@
         <v>22</v>
       </c>
       <c r="G54">
-        <v>-26.14945251063233</v>
+        <v>-27.74299036428698</v>
       </c>
       <c r="H54">
-        <v>2.207511626148317</v>
+        <v>0.6139737724936687</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -1978,16 +1978,16 @@
         <v>23</v>
       </c>
       <c r="G55">
-        <v>-25.74139976275207</v>
+        <v>-26.74219506351952</v>
       </c>
       <c r="H55">
-        <v>2.615564374028573</v>
+        <v>1.614769073261122</v>
       </c>
       <c r="I55">
-        <v>0.002722546360948808</v>
+        <v>0.001</v>
       </c>
       <c r="J55">
-        <v>9.261326443646645</v>
+        <v>5.061468655636036</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2036,10 +2036,10 @@
         <v>22</v>
       </c>
       <c r="G57">
-        <v>-6.888018315525379</v>
+        <v>-5.619561087991294</v>
       </c>
       <c r="H57">
-        <v>4.307893340721911</v>
+        <v>3.039436113187826</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2062,16 +2062,16 @@
         <v>23</v>
       </c>
       <c r="G58">
-        <v>-6.940544008042782</v>
+        <v>-6.358841086793142</v>
       </c>
       <c r="H58">
-        <v>4.360419033239314</v>
+        <v>3.778716111989674</v>
       </c>
       <c r="I58">
-        <v>0.1003470350482054</v>
+        <v>0.09465879553502221</v>
       </c>
       <c r="J58">
-        <v>5.424094029065443</v>
+        <v>4.844460247741853</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2120,10 +2120,10 @@
         <v>22</v>
       </c>
       <c r="G60">
-        <v>-4.340182019074399</v>
+        <v>-1.749476804006003</v>
       </c>
       <c r="H60">
-        <v>21.12447246861424</v>
+        <v>23.71517768368263</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2204,10 +2204,10 @@
         <v>22</v>
       </c>
       <c r="G63">
-        <v>-2.740166932561301</v>
+        <v>-2.658273994120623</v>
       </c>
       <c r="H63">
-        <v>0.4691359057993907</v>
+        <v>0.3872429673587119</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2230,16 +2230,16 @@
         <v>23</v>
       </c>
       <c r="G64">
-        <v>-2.666666666666671</v>
+        <v>-2.662470330393647</v>
       </c>
       <c r="H64">
-        <v>0.3956356399047607</v>
+        <v>0.3914393036317363</v>
       </c>
       <c r="I64">
-        <v>0.3868381550465201</v>
+        <v>0.2987785157810103</v>
       </c>
       <c r="J64">
-        <v>9.27312129748907</v>
+        <v>5.043351435174619</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2288,10 +2288,10 @@
         <v>22</v>
       </c>
       <c r="G66">
-        <v>-57.34220048224016</v>
+        <v>-58.82832630389451</v>
       </c>
       <c r="H66">
-        <v>4.064572870941831</v>
+        <v>2.578447049287483</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2314,16 +2314,16 @@
         <v>23</v>
       </c>
       <c r="G67">
-        <v>-54.54511190014166</v>
+        <v>-58.82832630389451</v>
       </c>
       <c r="H67">
-        <v>6.861661453040334</v>
+        <v>2.578447049287483</v>
       </c>
       <c r="I67">
         <v>0.001</v>
       </c>
       <c r="J67">
-        <v>8.360348690750994</v>
+        <v>8.315992646425135</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2372,10 +2372,10 @@
         <v>22</v>
       </c>
       <c r="G69">
-        <v>-19.56947061159492</v>
+        <v>-16.94198785852129</v>
       </c>
       <c r="H69">
-        <v>4.404121300928288</v>
+        <v>7.031604054001917</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2456,10 +2456,10 @@
         <v>22</v>
       </c>
       <c r="G72">
-        <v>1.078946189422229</v>
+        <v>4.27076693820225</v>
       </c>
       <c r="H72">
-        <v>2.181814320259722</v>
+        <v>1.010006428520299</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2482,16 +2482,16 @@
         <v>23</v>
       </c>
       <c r="G73">
-        <v>0.8264462809917319</v>
+        <v>2.548606609596991</v>
       </c>
       <c r="H73">
-        <v>2.434314228690219</v>
+        <v>0.7121539000849602</v>
       </c>
       <c r="I73">
-        <v>0.533886607841855</v>
+        <v>0.6704581009655978</v>
       </c>
       <c r="J73">
-        <v>9.717920735471186</v>
+        <v>5.776815458648815</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2540,10 +2540,10 @@
         <v>22</v>
       </c>
       <c r="G75">
-        <v>2.782615202862778</v>
+        <v>0.8114823295549364</v>
       </c>
       <c r="H75">
-        <v>6.560793354269863</v>
+        <v>8.531926227577705</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -2566,16 +2566,16 @@
         <v>23</v>
       </c>
       <c r="G76">
-        <v>2.451544735480415</v>
+        <v>0.8114823295549364</v>
       </c>
       <c r="H76">
-        <v>6.891863821652225</v>
+        <v>8.531926227577705</v>
       </c>
       <c r="I76">
-        <v>0.6776531336285638</v>
+        <v>0.5503335079946322</v>
       </c>
       <c r="J76">
-        <v>5.316198743380979</v>
+        <v>6.414677308281327</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -2624,10 +2624,10 @@
         <v>22</v>
       </c>
       <c r="G78">
-        <v>-16.21075837199487</v>
+        <v>-13.58846687292746</v>
       </c>
       <c r="H78">
-        <v>15.58647665104658</v>
+        <v>18.208768150114</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -2708,10 +2708,10 @@
         <v>22</v>
       </c>
       <c r="G81">
-        <v>-2.338121137486801</v>
+        <v>-0.3168159622798443</v>
       </c>
       <c r="H81">
-        <v>6.362066636350043</v>
+        <v>8.383371811557002</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -2734,16 +2734,16 @@
         <v>23</v>
       </c>
       <c r="G82">
-        <v>-2.454642475987193</v>
+        <v>-1.385729219133518</v>
       </c>
       <c r="H82">
-        <v>6.245545297849652</v>
+        <v>7.314458554703327</v>
       </c>
       <c r="I82">
-        <v>0.4063280475515493</v>
+        <v>0.4078364041737271</v>
       </c>
       <c r="J82">
-        <v>10.35710209019926</v>
+        <v>5.944424790175924</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -2792,10 +2792,10 @@
         <v>22</v>
       </c>
       <c r="G84">
-        <v>-13.95629209855609</v>
+        <v>-15.33749488275634</v>
       </c>
       <c r="H84">
-        <v>1.768009674920634</v>
+        <v>3.149212459120879</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -2818,16 +2818,16 @@
         <v>23</v>
       </c>
       <c r="G85">
-        <v>-13.6587084356192</v>
+        <v>-15.33749488275634</v>
       </c>
       <c r="H85">
-        <v>1.47042601198374</v>
+        <v>3.149212459120879</v>
       </c>
       <c r="I85">
-        <v>0.007551698746464627</v>
+        <v>0.01206422363196213</v>
       </c>
       <c r="J85">
-        <v>5.621121655288039</v>
+        <v>6.801315253106774</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -2876,10 +2876,10 @@
         <v>22</v>
       </c>
       <c r="G87">
-        <v>25.87394263072278</v>
+        <v>24.85999140804866</v>
       </c>
       <c r="H87">
-        <v>1.886057369277218</v>
+        <v>2.900008591951341</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -2902,16 +2902,16 @@
         <v>23</v>
       </c>
       <c r="G88">
-        <v>25.87394263072278</v>
+        <v>23.36708833150551</v>
       </c>
       <c r="H88">
-        <v>1.886057369277218</v>
+        <v>4.392911668494492</v>
       </c>
       <c r="I88">
         <v>0.999</v>
       </c>
       <c r="J88">
-        <v>5.603832645487631</v>
+        <v>4.927182409501452</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -2960,10 +2960,10 @@
         <v>22</v>
       </c>
       <c r="G90">
-        <v>-26.69593762345981</v>
+        <v>-26.65827706309963</v>
       </c>
       <c r="H90">
-        <v>7.583515574912301</v>
+        <v>7.621176135272485</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -2986,16 +2986,16 @@
         <v>23</v>
       </c>
       <c r="G91">
-        <v>-26.43678160919541</v>
+        <v>-26.54752933614752</v>
       </c>
       <c r="H91">
-        <v>7.842671589176696</v>
+        <v>7.73192386222459</v>
       </c>
       <c r="I91">
-        <v>0.002313520794631751</v>
+        <v>0.001</v>
       </c>
       <c r="J91">
-        <v>9.335308074074499</v>
+        <v>5.143590432278981</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3044,10 +3044,10 @@
         <v>22</v>
       </c>
       <c r="G93">
-        <v>-15.23314016592376</v>
+        <v>-14.29398428538185</v>
       </c>
       <c r="H93">
-        <v>4.567503588618866</v>
+        <v>5.506659469160779</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3070,16 +3070,16 @@
         <v>23</v>
       </c>
       <c r="G94">
-        <v>-15.45711318895895</v>
+        <v>-15.21150827172318</v>
       </c>
       <c r="H94">
-        <v>4.343530565583677</v>
+        <v>4.589135482819447</v>
       </c>
       <c r="I94">
-        <v>0.002292985927010862</v>
+        <v>0.001</v>
       </c>
       <c r="J94">
-        <v>5.45270068693277</v>
+        <v>4.887026893204637</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3128,10 +3128,10 @@
         <v>22</v>
       </c>
       <c r="G96">
-        <v>0.1996077540085479</v>
+        <v>2.412858983135079</v>
       </c>
       <c r="H96">
-        <v>0.6931577667713413</v>
+        <v>1.52009346235519</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3154,16 +3154,16 @@
         <v>23</v>
       </c>
       <c r="G97">
-        <v>0.1996077540085479</v>
+        <v>2.957900248132011</v>
       </c>
       <c r="H97">
-        <v>0.6931577667713413</v>
+        <v>2.065134727352122</v>
       </c>
       <c r="I97">
-        <v>0.5135974941786274</v>
+        <v>0.7226330607390499</v>
       </c>
       <c r="J97">
-        <v>5.855237004157829</v>
+        <v>5.007606455730596</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3212,10 +3212,10 @@
         <v>22</v>
       </c>
       <c r="G99">
-        <v>-20.58799263487226</v>
+        <v>-17.35244818736504</v>
       </c>
       <c r="H99">
-        <v>2.480492123938276</v>
+        <v>0.7550523235689468</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3238,16 +3238,16 @@
         <v>23</v>
       </c>
       <c r="G100">
-        <v>-20.59496567505721</v>
+        <v>-18.97370693121113</v>
       </c>
       <c r="H100">
-        <v>2.487465164123222</v>
+        <v>0.8662064202771376</v>
       </c>
       <c r="I100">
-        <v>0.01667791405759628</v>
+        <v>0.001</v>
       </c>
       <c r="J100">
-        <v>9.679113437771917</v>
+        <v>5.211290935515061</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -3296,10 +3296,10 @@
         <v>22</v>
       </c>
       <c r="G102">
-        <v>6.469545348436421</v>
+        <v>7.18984701924839</v>
       </c>
       <c r="H102">
-        <v>2.813897114474935</v>
+        <v>3.534198785286904</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -3322,16 +3322,16 @@
         <v>23</v>
       </c>
       <c r="G103">
-        <v>5.431611924252771</v>
+        <v>4.753829335475103</v>
       </c>
       <c r="H103">
-        <v>1.775963690291285</v>
+        <v>1.098181101513617</v>
       </c>
       <c r="I103">
-        <v>0.824784844198285</v>
+        <v>0.8050802767962357</v>
       </c>
       <c r="J103">
-        <v>5.816956485122046</v>
+        <v>5.528296292290408</v>
       </c>
     </row>
   </sheetData>
